--- a/data/GTR_data.xlsx
+++ b/data/GTR_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://griffitheduau.sharepoint.com/sites/PapayaFlavour9/Shared Documents/Research Projects/Josh_PhD_Flavour_Genomics/Project_Information/Experiments/Papaya_sensory_metabolomics/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://griffitheduau.sharepoint.com/sites/PapayaFlavour9/Shared Documents/Research Projects/Josh_PhD_Flavour_Genomics/Project_Information/Experiments/DATA_ANALYSIS/new_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D01C9FB-BF74-450B-ADDC-7528BE1A48FD}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D94CADD-ED6B-4730-925C-678F229FA807}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2nd_batch" sheetId="1" r:id="rId1"/>
@@ -1090,6 +1090,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1410,9 +1414,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1465,7 +1469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1506,7 +1510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G3" t="s">
         <v>27</v>
       </c>
@@ -1538,7 +1542,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G4" t="s">
         <v>27</v>
       </c>
@@ -1570,7 +1574,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1620,7 +1624,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1670,7 +1674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1720,7 +1724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1770,7 +1774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1820,7 +1824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>6</v>
       </c>
@@ -1870,7 +1874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>7</v>
       </c>
@@ -1920,7 +1924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1970,7 +1974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>9</v>
       </c>
@@ -2020,7 +2024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>10</v>
       </c>
@@ -2067,7 +2071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>11</v>
       </c>
@@ -2114,7 +2118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>12</v>
       </c>
@@ -2161,7 +2165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>13</v>
       </c>
@@ -2208,7 +2212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>14</v>
       </c>
@@ -2255,7 +2259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>15</v>
       </c>
@@ -2302,7 +2306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>16</v>
       </c>
@@ -2349,7 +2353,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>17</v>
       </c>
@@ -2396,7 +2400,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>18</v>
       </c>
@@ -2443,7 +2447,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>19</v>
       </c>
@@ -2490,7 +2494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2584,7 +2588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2631,7 +2635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2678,7 +2682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2725,7 +2729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2772,7 +2776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2819,7 +2823,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2866,7 +2870,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2913,7 +2917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>29</v>
       </c>
@@ -2960,7 +2964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>30</v>
       </c>
@@ -3007,7 +3011,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>31</v>
       </c>
@@ -3054,7 +3058,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3101,7 +3105,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3148,7 +3152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3195,7 +3199,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3242,7 +3246,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3289,7 +3293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3336,7 +3340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3383,7 +3387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3430,7 +3434,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3477,7 +3481,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3524,7 +3528,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3571,7 +3575,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3618,7 +3622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3665,7 +3669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3712,7 +3716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>46</v>
       </c>
@@ -3759,7 +3763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>47</v>
       </c>
@@ -3806,7 +3810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>48</v>
       </c>
@@ -3853,7 +3857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>49</v>
       </c>
@@ -3900,7 +3904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>50</v>
       </c>
@@ -3947,7 +3951,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>51</v>
       </c>
@@ -3994,7 +3998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>52</v>
       </c>
@@ -4041,7 +4045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>53</v>
       </c>
@@ -4088,7 +4092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>54</v>
       </c>
@@ -4135,7 +4139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>55</v>
       </c>
@@ -4182,7 +4186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>56</v>
       </c>
@@ -4229,7 +4233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>57</v>
       </c>
@@ -4276,7 +4280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>58</v>
       </c>
@@ -4323,7 +4327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>59</v>
       </c>
@@ -4370,7 +4374,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>60</v>
       </c>
@@ -4417,7 +4421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>61</v>
       </c>
@@ -4464,7 +4468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>62</v>
       </c>
@@ -4511,7 +4515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>63</v>
       </c>
@@ -4558,7 +4562,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>64</v>
       </c>
@@ -4605,7 +4609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>65</v>
       </c>
@@ -4652,7 +4656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>66</v>
       </c>
@@ -4699,7 +4703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>67</v>
       </c>
@@ -4746,7 +4750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>68</v>
       </c>
@@ -4793,7 +4797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>69</v>
       </c>
@@ -4840,7 +4844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>70</v>
       </c>
@@ -4887,7 +4891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>71</v>
       </c>
@@ -4934,7 +4938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>72</v>
       </c>
@@ -4981,7 +4985,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>73</v>
       </c>
@@ -5028,7 +5032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>74</v>
       </c>
@@ -5075,7 +5079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>75</v>
       </c>
@@ -5122,7 +5126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>76</v>
       </c>
@@ -5169,7 +5173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>77</v>
       </c>
@@ -5216,7 +5220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>78</v>
       </c>
@@ -5263,7 +5267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>79</v>
       </c>
@@ -5310,7 +5314,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>80</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>81</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>82</v>
       </c>
@@ -5451,7 +5455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>83</v>
       </c>
@@ -5498,7 +5502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>84</v>
       </c>
@@ -5545,7 +5549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>85</v>
       </c>
@@ -5592,7 +5596,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>86</v>
       </c>
@@ -5639,7 +5643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>87</v>
       </c>
@@ -5686,7 +5690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>190</v>
       </c>
@@ -5694,7 +5698,7 @@
         <v>49.04</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>43.66</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>192</v>
       </c>
@@ -5710,7 +5714,7 @@
         <v>38.03</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>193</v>
       </c>
@@ -5718,7 +5722,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>194</v>
       </c>
@@ -5734,9 +5738,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690C8EB8-1165-4F42-8A59-6BF6A3546C05}">
   <dimension ref="A1:Q181"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5789,7 +5793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -5830,7 +5834,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G3" t="s">
         <v>27</v>
       </c>
@@ -5862,7 +5866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G4" t="s">
         <v>27</v>
       </c>
@@ -5894,7 +5898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5938,7 +5942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
@@ -5982,7 +5986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3</v>
       </c>
@@ -6026,7 +6030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
@@ -6070,7 +6074,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>5</v>
       </c>
@@ -6114,7 +6118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6158,7 +6162,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>7</v>
       </c>
@@ -6202,7 +6206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>8</v>
       </c>
@@ -6246,7 +6250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>9</v>
       </c>
@@ -6290,7 +6294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>10</v>
       </c>
@@ -6334,7 +6338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>11</v>
       </c>
@@ -6378,7 +6382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>12</v>
       </c>
@@ -6422,7 +6426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>13</v>
       </c>
@@ -6466,7 +6470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>14</v>
       </c>
@@ -6510,7 +6514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>15</v>
       </c>
@@ -6554,7 +6558,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>16</v>
       </c>
@@ -6598,7 +6602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>17</v>
       </c>
@@ -6642,7 +6646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>18</v>
       </c>
@@ -6689,7 +6693,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>19</v>
       </c>
@@ -6736,7 +6740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20</v>
       </c>
@@ -6783,7 +6787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>21</v>
       </c>
@@ -6830,7 +6834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>22</v>
       </c>
@@ -6877,7 +6881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>23</v>
       </c>
@@ -6927,7 +6931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>24</v>
       </c>
@@ -6977,7 +6981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>25</v>
       </c>
@@ -7027,7 +7031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>26</v>
       </c>
@@ -7077,7 +7081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>27</v>
       </c>
@@ -7127,7 +7131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>28</v>
       </c>
@@ -7177,7 +7181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>29</v>
       </c>
@@ -7227,7 +7231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>30</v>
       </c>
@@ -7277,7 +7281,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>31</v>
       </c>
@@ -7327,7 +7331,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>32</v>
       </c>
@@ -7374,7 +7378,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>33</v>
       </c>
@@ -7421,7 +7425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>34</v>
       </c>
@@ -7468,7 +7472,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>35</v>
       </c>
@@ -7515,7 +7519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>36</v>
       </c>
@@ -7562,7 +7566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>37</v>
       </c>
@@ -7609,7 +7613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>38</v>
       </c>
@@ -7656,7 +7660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>39</v>
       </c>
@@ -7703,7 +7707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>40</v>
       </c>
@@ -7750,7 +7754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>41</v>
       </c>
@@ -7797,7 +7801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>42</v>
       </c>
@@ -7844,7 +7848,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>43</v>
       </c>
@@ -7891,7 +7895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>44</v>
       </c>
@@ -7938,7 +7942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>45</v>
       </c>
@@ -7985,7 +7989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>46</v>
       </c>
@@ -8032,7 +8036,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>47</v>
       </c>
@@ -8079,7 +8083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>48</v>
       </c>
@@ -8126,7 +8130,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>49</v>
       </c>
@@ -8173,7 +8177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>50</v>
       </c>
@@ -8220,7 +8224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>51</v>
       </c>
@@ -8267,7 +8271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>52</v>
       </c>
@@ -8314,7 +8318,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>53</v>
       </c>
@@ -8361,7 +8365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>54</v>
       </c>
@@ -8408,7 +8412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>55</v>
       </c>
@@ -8455,7 +8459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>56</v>
       </c>
@@ -8502,7 +8506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>57</v>
       </c>
@@ -8549,7 +8553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>58</v>
       </c>
@@ -8596,7 +8600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>59</v>
       </c>
@@ -8643,7 +8647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>60</v>
       </c>
@@ -8690,7 +8694,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>61</v>
       </c>
@@ -8737,7 +8741,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>62</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>63</v>
       </c>
@@ -8831,7 +8835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>64</v>
       </c>
@@ -8878,7 +8882,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>65</v>
       </c>
@@ -8925,7 +8929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>66</v>
       </c>
@@ -8972,7 +8976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>67</v>
       </c>
@@ -9019,7 +9023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>68</v>
       </c>
@@ -9066,7 +9070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>69</v>
       </c>
@@ -9113,7 +9117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>70</v>
       </c>
@@ -9160,7 +9164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>71</v>
       </c>
@@ -9207,7 +9211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>72</v>
       </c>
@@ -9254,7 +9258,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>73</v>
       </c>
@@ -9301,7 +9305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>74</v>
       </c>
@@ -9348,7 +9352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>75</v>
       </c>
@@ -9395,7 +9399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>76</v>
       </c>
@@ -9442,7 +9446,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>77</v>
       </c>
@@ -9489,7 +9493,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>78</v>
       </c>
@@ -9536,7 +9540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>79</v>
       </c>
@@ -9583,7 +9587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>80</v>
       </c>
@@ -9630,7 +9634,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>81</v>
       </c>
@@ -9677,7 +9681,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>82</v>
       </c>
@@ -9724,7 +9728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>83</v>
       </c>
@@ -9771,7 +9775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>84</v>
       </c>
@@ -9818,7 +9822,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>85</v>
       </c>
@@ -9865,7 +9869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>86</v>
       </c>
@@ -9912,7 +9916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>87</v>
       </c>
@@ -9959,7 +9963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>88</v>
       </c>
@@ -10006,7 +10010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>89</v>
       </c>
@@ -10053,7 +10057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>90</v>
       </c>
@@ -10100,7 +10104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>91</v>
       </c>
@@ -10147,7 +10151,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>92</v>
       </c>
@@ -10194,7 +10198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>93</v>
       </c>
@@ -10241,7 +10245,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>94</v>
       </c>
@@ -10288,7 +10292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>95</v>
       </c>
@@ -10335,7 +10339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>96</v>
       </c>
@@ -10382,7 +10386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>97</v>
       </c>
@@ -10429,7 +10433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>98</v>
       </c>
@@ -10476,7 +10480,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>99</v>
       </c>
@@ -10523,7 +10527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>100</v>
       </c>
@@ -10570,7 +10574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>101</v>
       </c>
@@ -10617,7 +10621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>102</v>
       </c>
@@ -10664,7 +10668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>103</v>
       </c>
@@ -10711,7 +10715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>104</v>
       </c>
@@ -10758,7 +10762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>105</v>
       </c>
@@ -10805,7 +10809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>106</v>
       </c>
@@ -10852,7 +10856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>107</v>
       </c>
@@ -10899,7 +10903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>108</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>109</v>
       </c>
@@ -10993,7 +10997,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>110</v>
       </c>
@@ -11040,7 +11044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>111</v>
       </c>
@@ -11087,7 +11091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>112</v>
       </c>
@@ -11134,7 +11138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>113</v>
       </c>
@@ -11181,7 +11185,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>114</v>
       </c>
@@ -11228,7 +11232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>115</v>
       </c>
@@ -11275,7 +11279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>116</v>
       </c>
@@ -11322,7 +11326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>117</v>
       </c>
@@ -11369,7 +11373,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>118</v>
       </c>
@@ -11416,7 +11420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>119</v>
       </c>
@@ -11463,7 +11467,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>120</v>
       </c>
@@ -11510,7 +11514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>121</v>
       </c>
@@ -11557,7 +11561,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>122</v>
       </c>
@@ -11604,7 +11608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>123</v>
       </c>
@@ -11651,7 +11655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>124</v>
       </c>
@@ -11698,7 +11702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>125</v>
       </c>
@@ -11745,7 +11749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>126</v>
       </c>
@@ -11792,7 +11796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>127</v>
       </c>
@@ -11839,7 +11843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>128</v>
       </c>
@@ -11886,7 +11890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>129</v>
       </c>
@@ -11933,7 +11937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>130</v>
       </c>
@@ -11980,7 +11984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>131</v>
       </c>
@@ -12027,7 +12031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>132</v>
       </c>
@@ -12074,7 +12078,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>133</v>
       </c>
@@ -12121,7 +12125,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>134</v>
       </c>
@@ -12168,7 +12172,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>135</v>
       </c>
@@ -12215,7 +12219,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>136</v>
       </c>
@@ -12262,7 +12266,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>137</v>
       </c>
@@ -12309,7 +12313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>138</v>
       </c>
@@ -12356,7 +12360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>139</v>
       </c>
@@ -12403,7 +12407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>140</v>
       </c>
@@ -12450,7 +12454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>141</v>
       </c>
@@ -12497,7 +12501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>142</v>
       </c>
@@ -12544,7 +12548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>143</v>
       </c>
@@ -12591,7 +12595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>144</v>
       </c>
@@ -12638,7 +12642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>145</v>
       </c>
@@ -12685,7 +12689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>146</v>
       </c>
@@ -12732,7 +12736,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>147</v>
       </c>
@@ -12779,7 +12783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>148</v>
       </c>
@@ -12826,7 +12830,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>149</v>
       </c>
@@ -12873,7 +12877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>150</v>
       </c>
@@ -12920,7 +12924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>151</v>
       </c>
@@ -12967,7 +12971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>152</v>
       </c>
@@ -13014,7 +13018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>153</v>
       </c>
@@ -13061,7 +13065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>154</v>
       </c>
@@ -13108,7 +13112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>155</v>
       </c>
@@ -13155,7 +13159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>156</v>
       </c>
@@ -13202,7 +13206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>157</v>
       </c>
@@ -13249,7 +13253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>158</v>
       </c>
@@ -13296,7 +13300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>159</v>
       </c>
@@ -13343,7 +13347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>160</v>
       </c>
@@ -13390,7 +13394,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>161</v>
       </c>
@@ -13437,7 +13441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>162</v>
       </c>
@@ -13484,7 +13488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>163</v>
       </c>
@@ -13531,7 +13535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>164</v>
       </c>
@@ -13578,7 +13582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>165</v>
       </c>
@@ -13625,7 +13629,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>166</v>
       </c>
@@ -13672,7 +13676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>167</v>
       </c>
@@ -13719,7 +13723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>168</v>
       </c>
@@ -13766,7 +13770,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>169</v>
       </c>
@@ -13813,7 +13817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>170</v>
       </c>
@@ -13860,7 +13864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>171</v>
       </c>
@@ -13907,7 +13911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>172</v>
       </c>
@@ -13954,7 +13958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>190</v>
       </c>
@@ -13962,7 +13966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>191</v>
       </c>
@@ -13970,7 +13974,7 @@
         <v>37.24</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>192</v>
       </c>
@@ -13978,7 +13982,7 @@
         <v>24.55</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>193</v>
       </c>
@@ -13986,7 +13990,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>194</v>
       </c>
@@ -14002,9 +14006,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E9BC80-F245-46A7-AA82-4D0FCFEEEFB8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>325</v>
       </c>
@@ -14012,7 +14016,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>327</v>
       </c>
@@ -14023,7 +14027,7 @@
         <v>0.99940329149999996</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>328</v>
       </c>
@@ -14042,9 +14046,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD16DB7-9EF6-4A8D-B729-C801802222E7}">
   <dimension ref="A1:B181"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>330</v>
       </c>
@@ -14052,7 +14056,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>195</v>
       </c>
@@ -14060,7 +14064,7 @@
         <v>0.14849999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>195</v>
       </c>
@@ -14068,7 +14072,7 @@
         <v>0.74990000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>196</v>
       </c>
@@ -14076,7 +14080,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>196</v>
       </c>
@@ -14084,7 +14088,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>195</v>
       </c>
@@ -14092,7 +14096,7 @@
         <v>0.64739999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>195</v>
       </c>
@@ -14100,7 +14104,7 @@
         <v>0.83030000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>195</v>
       </c>
@@ -14108,7 +14112,7 @@
         <v>0.55910000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>197</v>
       </c>
@@ -14116,7 +14120,7 @@
         <v>0.97989999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>198</v>
       </c>
@@ -14124,7 +14128,7 @@
         <v>0.31709999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>199</v>
       </c>
@@ -14132,7 +14136,7 @@
         <v>0.30380000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>200</v>
       </c>
@@ -14140,7 +14144,7 @@
         <v>2.4569999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>201</v>
       </c>
@@ -14148,7 +14152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -14156,7 +14160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>202</v>
       </c>
@@ -14164,7 +14168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>203</v>
       </c>
@@ -14172,7 +14176,7 @@
         <v>0.32750000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>204</v>
       </c>
@@ -14180,7 +14184,7 @@
         <v>0.33239999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>205</v>
       </c>
@@ -14188,7 +14192,7 @@
         <v>0.32750000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>206</v>
       </c>
@@ -14196,7 +14200,7 @@
         <v>0.4466</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>207</v>
       </c>
@@ -14204,7 +14208,7 @@
         <v>0.63070000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>208</v>
       </c>
@@ -14212,7 +14216,7 @@
         <v>0.97209999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>209</v>
       </c>
@@ -14220,7 +14224,7 @@
         <v>1.9633</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>210</v>
       </c>
@@ -14228,7 +14232,7 @@
         <v>3.2852000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -14236,7 +14240,7 @@
         <v>0.53820000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -14244,7 +14248,7 @@
         <v>0.80169999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -14252,7 +14256,7 @@
         <v>1.4726999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -14260,7 +14264,7 @@
         <v>2.8214000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -14268,7 +14272,7 @@
         <v>5.7304000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -14276,7 +14280,7 @@
         <v>9.4809000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -14284,7 +14288,7 @@
         <v>24.165800000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -14292,7 +14296,7 @@
         <v>48.059899999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -14300,7 +14304,7 @@
         <v>101.179</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>211</v>
       </c>
@@ -14308,7 +14312,7 @@
         <v>1.4859</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>213</v>
       </c>
@@ -14316,7 +14320,7 @@
         <v>3.4807000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>215</v>
       </c>
@@ -14324,7 +14328,7 @@
         <v>6.7629999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>217</v>
       </c>
@@ -14332,7 +14336,7 @@
         <v>29.258600000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>219</v>
       </c>
@@ -14340,7 +14344,7 @@
         <v>6.1670999999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>221</v>
       </c>
@@ -14348,7 +14352,7 @@
         <v>3.7397</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>223</v>
       </c>
@@ -14356,7 +14360,7 @@
         <v>4.6485000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>225</v>
       </c>
@@ -14364,7 +14368,7 @@
         <v>0.56659999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>227</v>
       </c>
@@ -14372,7 +14376,7 @@
         <v>7.8754999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>229</v>
       </c>
@@ -14380,7 +14384,7 @@
         <v>5.6856999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>231</v>
       </c>
@@ -14388,7 +14392,7 @@
         <v>14.418200000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>233</v>
       </c>
@@ -14396,7 +14400,7 @@
         <v>4.4664000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>235</v>
       </c>
@@ -14404,7 +14408,7 @@
         <v>4.1428000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>237</v>
       </c>
@@ -14412,7 +14416,7 @@
         <v>5.8907999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>239</v>
       </c>
@@ -14420,7 +14424,7 @@
         <v>0.61450000000000005</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>241</v>
       </c>
@@ -14428,7 +14432,7 @@
         <v>2.4830000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -14436,7 +14440,7 @@
         <v>1.2633000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>243</v>
       </c>
@@ -14444,7 +14448,7 @@
         <v>1.2528999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>245</v>
       </c>
@@ -14452,7 +14456,7 @@
         <v>0.58609999999999995</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>247</v>
       </c>
@@ -14460,7 +14464,7 @@
         <v>33.123399999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>249</v>
       </c>
@@ -14468,7 +14472,7 @@
         <v>1.2524999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>251</v>
       </c>
@@ -14476,7 +14480,7 @@
         <v>1.2405999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>253</v>
       </c>
@@ -14484,7 +14488,7 @@
         <v>4.891</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>255</v>
       </c>
@@ -14492,7 +14496,7 @@
         <v>5.8524000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>257</v>
       </c>
@@ -14500,7 +14504,7 @@
         <v>1.593</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>259</v>
       </c>
@@ -14508,7 +14512,7 @@
         <v>4.9802</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -14516,7 +14520,7 @@
         <v>1.2486999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>261</v>
       </c>
@@ -14524,7 +14528,7 @@
         <v>1.6364000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>263</v>
       </c>
@@ -14532,7 +14536,7 @@
         <v>41.667499999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>265</v>
       </c>
@@ -14540,7 +14544,7 @@
         <v>4.7382</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>267</v>
       </c>
@@ -14548,7 +14552,7 @@
         <v>0.64559999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>269</v>
       </c>
@@ -14556,7 +14560,7 @@
         <v>2.0084</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>271</v>
       </c>
@@ -14564,7 +14568,7 @@
         <v>54.0319</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>273</v>
       </c>
@@ -14572,7 +14576,7 @@
         <v>0.56159999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>275</v>
       </c>
@@ -14580,7 +14584,7 @@
         <v>3.2702</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>277</v>
       </c>
@@ -14588,7 +14592,7 @@
         <v>9.4758999999999993</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -14596,7 +14600,7 @@
         <v>1.3535999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>279</v>
       </c>
@@ -14604,7 +14608,7 @@
         <v>1.3661000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>281</v>
       </c>
@@ -14612,7 +14616,7 @@
         <v>1.5693999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>283</v>
       </c>
@@ -14620,7 +14624,7 @@
         <v>0.38540000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>285</v>
       </c>
@@ -14628,7 +14632,7 @@
         <v>2.1724000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>287</v>
       </c>
@@ -14636,7 +14640,7 @@
         <v>32.398600000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>289</v>
       </c>
@@ -14644,7 +14648,7 @@
         <v>1.2696000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>291</v>
       </c>
@@ -14652,7 +14656,7 @@
         <v>5.6306000000000003</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>293</v>
       </c>
@@ -14660,7 +14664,7 @@
         <v>25.100100000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>295</v>
       </c>
@@ -14668,7 +14672,7 @@
         <v>18.581900000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>57</v>
       </c>
@@ -14676,7 +14680,7 @@
         <v>1.2618</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>297</v>
       </c>
@@ -14684,7 +14688,7 @@
         <v>9.8656000000000006</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>299</v>
       </c>
@@ -14692,7 +14696,7 @@
         <v>2.0644</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>301</v>
       </c>
@@ -14700,7 +14704,7 @@
         <v>2.4077000000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>303</v>
       </c>
@@ -14708,7 +14712,7 @@
         <v>7.8875000000000002</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>305</v>
       </c>
@@ -14716,7 +14720,7 @@
         <v>4.7670000000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>307</v>
       </c>
@@ -14724,7 +14728,7 @@
         <v>1.4850000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>309</v>
       </c>
@@ -14732,7 +14736,7 @@
         <v>6.9721000000000002</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>311</v>
       </c>
@@ -14740,7 +14744,7 @@
         <v>5.5252999999999997</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>313</v>
       </c>
@@ -14748,7 +14752,7 @@
         <v>5.1928999999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>57</v>
       </c>
@@ -14756,7 +14760,7 @@
         <v>1.2412000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>315</v>
       </c>
@@ -14764,7 +14768,7 @@
         <v>24.903500000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>317</v>
       </c>
@@ -14772,7 +14776,7 @@
         <v>1.3638999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>57</v>
       </c>
@@ -14780,7 +14784,7 @@
         <v>0.70940000000000003</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>319</v>
       </c>
@@ -14788,7 +14792,7 @@
         <v>85.317599999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>321</v>
       </c>
@@ -14796,7 +14800,7 @@
         <v>0.3337</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>28</v>
       </c>
@@ -14804,7 +14808,7 @@
         <v>0.30590000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>32</v>
       </c>
@@ -14812,7 +14816,7 @@
         <v>0.5484</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>34</v>
       </c>
@@ -14820,7 +14824,7 @@
         <v>1.0206999999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>36</v>
       </c>
@@ -14828,7 +14832,7 @@
         <v>2.8231999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>38</v>
       </c>
@@ -14836,7 +14840,7 @@
         <v>5.6637000000000004</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -14844,7 +14848,7 @@
         <v>10.1387</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>42</v>
       </c>
@@ -14852,7 +14856,7 @@
         <v>22.924399999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>44</v>
       </c>
@@ -14860,7 +14864,7 @@
         <v>50.723700000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>46</v>
       </c>
@@ -14868,7 +14872,7 @@
         <v>100.10129999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>48</v>
       </c>
@@ -14876,7 +14880,7 @@
         <v>4.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>51</v>
       </c>
@@ -14884,7 +14888,7 @@
         <v>1.44E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>53</v>
       </c>
@@ -14892,7 +14896,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -14900,7 +14904,7 @@
         <v>0.85150000000000003</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>57</v>
       </c>
@@ -14908,7 +14912,7 @@
         <v>0.99619999999999997</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>58</v>
       </c>
@@ -14916,7 +14920,7 @@
         <v>0.1431</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>60</v>
       </c>
@@ -14924,7 +14928,7 @@
         <v>2.0627</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>62</v>
       </c>
@@ -14932,7 +14936,7 @@
         <v>0.59360000000000002</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>64</v>
       </c>
@@ -14940,7 +14944,7 @@
         <v>0.4385</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>66</v>
       </c>
@@ -14948,7 +14952,7 @@
         <v>7.7401999999999997</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>68</v>
       </c>
@@ -14956,7 +14960,7 @@
         <v>0.34570000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>70</v>
       </c>
@@ -14964,7 +14968,7 @@
         <v>0.41349999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>72</v>
       </c>
@@ -14972,7 +14976,7 @@
         <v>6.9474999999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>74</v>
       </c>
@@ -14980,7 +14984,7 @@
         <v>8.0822000000000003</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>57</v>
       </c>
@@ -14988,7 +14992,7 @@
         <v>1.1206</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>76</v>
       </c>
@@ -14996,7 +15000,7 @@
         <v>0.307</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>78</v>
       </c>
@@ -15004,7 +15008,7 @@
         <v>9.6579999999999995</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>80</v>
       </c>
@@ -15012,7 +15016,7 @@
         <v>0.9708</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>82</v>
       </c>
@@ -15020,7 +15024,7 @@
         <v>1.5347999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -15028,7 +15032,7 @@
         <v>0.84640000000000004</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>86</v>
       </c>
@@ -15036,7 +15040,7 @@
         <v>1.6075999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>88</v>
       </c>
@@ -15044,7 +15048,7 @@
         <v>2.3222</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>90</v>
       </c>
@@ -15052,7 +15056,7 @@
         <v>0.83630000000000004</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>92</v>
       </c>
@@ -15060,7 +15064,7 @@
         <v>8.9214000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>57</v>
       </c>
@@ -15068,7 +15072,7 @@
         <v>1.1427</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -15076,7 +15080,7 @@
         <v>9.1207999999999991</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>96</v>
       </c>
@@ -15084,7 +15088,7 @@
         <v>10.625400000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>98</v>
       </c>
@@ -15092,7 +15096,7 @@
         <v>3.4203999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>100</v>
       </c>
@@ -15100,7 +15104,7 @@
         <v>7.9520999999999997</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>102</v>
       </c>
@@ -15108,7 +15112,7 @@
         <v>8.6903000000000006</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>104</v>
       </c>
@@ -15116,7 +15120,7 @@
         <v>2.2385999999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>106</v>
       </c>
@@ -15124,7 +15128,7 @@
         <v>2.0634999999999999</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>108</v>
       </c>
@@ -15132,7 +15136,7 @@
         <v>0.38300000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>110</v>
       </c>
@@ -15140,7 +15144,7 @@
         <v>1.0146999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>57</v>
       </c>
@@ -15148,7 +15152,7 @@
         <v>1.1435</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>112</v>
       </c>
@@ -15156,7 +15160,7 @@
         <v>6.9888000000000003</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>114</v>
       </c>
@@ -15164,7 +15168,7 @@
         <v>2.86E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>116</v>
       </c>
@@ -15172,7 +15176,7 @@
         <v>1.0281</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>118</v>
       </c>
@@ -15180,7 +15184,7 @@
         <v>15.123699999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>120</v>
       </c>
@@ -15188,7 +15192,7 @@
         <v>8.0342000000000002</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>122</v>
       </c>
@@ -15196,7 +15200,7 @@
         <v>1.492</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>124</v>
       </c>
@@ -15204,7 +15208,7 @@
         <v>18.939800000000002</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>126</v>
       </c>
@@ -15212,7 +15216,7 @@
         <v>10.082100000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>128</v>
       </c>
@@ -15220,7 +15224,7 @@
         <v>3.8309000000000002</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>57</v>
       </c>
@@ -15228,7 +15232,7 @@
         <v>1.0449999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>130</v>
       </c>
@@ -15236,7 +15240,7 @@
         <v>3.726</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>132</v>
       </c>
@@ -15244,7 +15248,7 @@
         <v>9.0700000000000003E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>134</v>
       </c>
@@ -15252,7 +15256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>136</v>
       </c>
@@ -15260,7 +15264,7 @@
         <v>7.7799999999999994E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>138</v>
       </c>
@@ -15268,7 +15272,7 @@
         <v>0.75260000000000005</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>140</v>
       </c>
@@ -15276,7 +15280,7 @@
         <v>0.18079999999999999</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>142</v>
       </c>
@@ -15284,7 +15288,7 @@
         <v>7.1199999999999999E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>144</v>
       </c>
@@ -15292,7 +15296,7 @@
         <v>0.40789999999999998</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>146</v>
       </c>
@@ -15300,7 +15304,7 @@
         <v>0.45240000000000002</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>148</v>
       </c>
@@ -15308,7 +15312,7 @@
         <v>0.5615</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>57</v>
       </c>
@@ -15316,7 +15320,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>150</v>
       </c>
@@ -15324,7 +15328,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>152</v>
       </c>
@@ -15332,7 +15336,7 @@
         <v>1.204</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>154</v>
       </c>
@@ -15340,7 +15344,7 @@
         <v>0.42820000000000003</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>156</v>
       </c>
@@ -15348,7 +15352,7 @@
         <v>0.40229999999999999</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>158</v>
       </c>
@@ -15356,7 +15360,7 @@
         <v>0.35439999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>160</v>
       </c>
@@ -15364,7 +15368,7 @@
         <v>1.0038</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>162</v>
       </c>
@@ -15372,7 +15376,7 @@
         <v>0.20280000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>164</v>
       </c>
@@ -15380,7 +15384,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -15388,7 +15392,7 @@
         <v>2.4899999999999999E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>57</v>
       </c>
@@ -15396,7 +15400,7 @@
         <v>1.1420999999999999</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>168</v>
       </c>
@@ -15404,7 +15408,7 @@
         <v>0.1527</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>170</v>
       </c>
@@ -15412,7 +15416,7 @@
         <v>0.26369999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>172</v>
       </c>
@@ -15420,7 +15424,7 @@
         <v>0.27529999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>174</v>
       </c>
@@ -15428,7 +15432,7 @@
         <v>3.7073999999999998</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -15436,7 +15440,7 @@
         <v>8.2992000000000008</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>178</v>
       </c>
@@ -15444,7 +15448,7 @@
         <v>7.9066000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>180</v>
       </c>
@@ -15452,7 +15456,7 @@
         <v>0.66359999999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>182</v>
       </c>
@@ -15460,7 +15464,7 @@
         <v>9.2500999999999998</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>184</v>
       </c>
@@ -15468,7 +15472,7 @@
         <v>1.9994000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>57</v>
       </c>
@@ -15476,7 +15480,7 @@
         <v>1.1913</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>186</v>
       </c>
@@ -15484,7 +15488,7 @@
         <v>7.4015000000000004</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -15499,6 +15503,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="312aad96-96f5-469b-aa89-ed1395b471aa">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59bdd577-87e5-408b-82ee-b778416b7e33">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="312aad96-96f5-469b-aa89-ed1395b471aa" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045EEA7378D4F9D4D971E372262DEEEF3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f2706c894104d0f6c0f0e43ae247914a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="59bdd577-87e5-408b-82ee-b778416b7e33" xmlns:ns3="312aad96-96f5-469b-aa89-ed1395b471aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f8d303bca06c7c8e692b5b5fda65fe5" ns2:_="" ns3:_="">
     <xsd:import namespace="59bdd577-87e5-408b-82ee-b778416b7e33"/>
@@ -15753,24 +15775,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="312aad96-96f5-469b-aa89-ed1395b471aa">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59bdd577-87e5-408b-82ee-b778416b7e33">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="312aad96-96f5-469b-aa89-ed1395b471aa" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -15781,6 +15785,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A2F657F-8CC2-4778-8C3C-CEE897C63E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="312aad96-96f5-469b-aa89-ed1395b471aa"/>
+    <ds:schemaRef ds:uri="59bdd577-87e5-408b-82ee-b778416b7e33"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B124CC0-84A5-4028-9734-0D44EEF3F61D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15799,17 +15814,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A2F657F-8CC2-4778-8C3C-CEE897C63E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="312aad96-96f5-469b-aa89-ed1395b471aa"/>
-    <ds:schemaRef ds:uri="59bdd577-87e5-408b-82ee-b778416b7e33"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1EF4DB-A2C5-4EC7-8561-6D41F8A0F27E}">
   <ds:schemaRefs>
@@ -15820,6 +15824,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{c9f92db8-2851-4df9-9d12-fab52f5b1415}" enabled="1" method="Standard" siteId="{5a7cc8ab-a4dc-4f9b-bf60-66714049ad62}" contentBits="0" removed="0"/>
+  <clbl:label id="{c9f92db8-2851-4df9-9d12-fab52f5b1415}" enabled="1" method="Standard" siteId="{5a7cc8ab-a4dc-4f9b-bf60-66714049ad62}" removed="0"/>
 </clbl:labelList>
 </file>